--- a/ARC_simple.xlsx
+++ b/ARC_simple.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA09373-ECAA-4603-BE7E-41063F6B09BB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83BEE79B-3340-4DEA-8D70-8B445B7FBCB8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15200" windowHeight="6930" activeTab="5" xr2:uid="{B141029A-C238-484B-8693-F95FDEE8D83E}"/>
   </bookViews>
@@ -20,9 +20,10 @@
     <sheet name="tech_pot" sheetId="9" r:id="rId5"/>
     <sheet name="market" sheetId="8" r:id="rId6"/>
     <sheet name="Feuil4" sheetId="12" r:id="rId7"/>
+    <sheet name="dist_col" sheetId="13" r:id="rId8"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
   <si>
     <t>A</t>
   </si>
@@ -154,6 +155,9 @@
   </si>
   <si>
     <t>Site</t>
+  </si>
+  <si>
+    <t>dist_col</t>
   </si>
 </sst>
 </file>
@@ -1602,4 +1606,55 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B83A381-22AF-46A0-9DDF-5B74B916E2B3}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="str">
+        <f>tech_pot!A2</f>
+        <v>Compiègne</v>
+      </c>
+      <c r="B2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="str">
+        <f>tech_pot!A3</f>
+        <v>Venette</v>
+      </c>
+      <c r="B3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="str">
+        <f>tech_pot!A4</f>
+        <v>Jaux</v>
+      </c>
+      <c r="B4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="str">
+        <f>tech_pot!A5</f>
+        <v>Armancourt</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>